--- a/diseases/d036/2026-2029.xlsx
+++ b/diseases/d036/2026-2029.xlsx
@@ -2019,6 +2019,154 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D036</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>schistosomiasis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Schistosomiasis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D036</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Schistosomiasis</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>血吸虫病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.0001415514231387749</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2052,7 +2200,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2283,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2145,7 +2293,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2197,7 +2345,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d036/2026-2029.xlsx
+++ b/diseases/d036/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4448,6 +4583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4978,6 +5118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5114,6 +5259,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5250,6 +5400,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5386,6 +5541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5522,6 +5682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5658,6 +5823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5794,6 +5964,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5930,6 +6105,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6066,6 +6246,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6202,6 +6387,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6338,6 +6528,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6474,6 +6669,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6610,6 +6810,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6746,6 +6951,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6882,6 +7092,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7018,6 +7233,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7154,6 +7374,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7290,6 +7515,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7426,6 +7656,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7562,6 +7797,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7698,6 +7938,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7834,6 +8079,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7970,6 +8220,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8106,6 +8361,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8242,6 +8502,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8378,6 +8643,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8514,6 +8784,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8653,6 +8928,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9183,6 +9463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9319,6 +9604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9455,6 +9745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9591,6 +9886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9727,6 +10027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9863,6 +10168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9999,6 +10309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10135,6 +10450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10271,6 +10591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10407,6 +10732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10543,6 +10873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10679,6 +11014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10815,6 +11155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10951,6 +11296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11087,6 +11437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11223,6 +11578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11359,6 +11719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11495,6 +11860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11631,6 +12001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11767,6 +12142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11903,6 +12283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12039,6 +12424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12175,6 +12565,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12311,6 +12706,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12447,6 +12847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12583,6 +12988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12719,6 +13129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12858,6 +13273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13003,6 +13423,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13148,6 +13573,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13284,6 +13714,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13420,6 +13855,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13556,6 +13996,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13692,6 +14137,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13828,6 +14278,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13964,6 +14419,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14100,6 +14560,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14236,6 +14701,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14372,6 +14842,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14508,6 +14983,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14644,6 +15124,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14780,6 +15265,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14916,6 +15406,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15052,6 +15547,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15188,6 +15688,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15324,6 +15829,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15460,6 +15970,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15596,6 +16111,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15732,6 +16252,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15868,6 +16393,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16004,6 +16534,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16140,6 +16675,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16276,6 +16816,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16412,6 +16957,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16548,6 +17098,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16684,6 +17239,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16823,6 +17383,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16968,6 +17533,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17113,6 +17683,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17249,6 +17824,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17385,6 +17965,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17521,6 +18106,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17657,6 +18247,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17793,6 +18388,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17929,6 +18529,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18065,6 +18670,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18201,6 +18811,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18337,6 +18952,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18473,6 +19093,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18609,6 +19234,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18745,6 +19375,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18881,6 +19516,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19017,6 +19657,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19153,6 +19798,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19289,6 +19939,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19425,6 +20080,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19561,6 +20221,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19697,6 +20362,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19833,6 +20503,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19969,6 +20644,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20105,6 +20785,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20241,6 +20926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20377,6 +21067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20513,6 +21208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20649,6 +21349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20788,6 +21493,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21706,6 +22416,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24964,6 +25679,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28610,6 +29330,11 @@
       <c r="S188" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">

--- a/diseases/d036/2026-2029.xlsx
+++ b/diseases/d036/2026-2029.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,13 +785,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
@@ -797,6 +812,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>web</t>
@@ -812,7 +832,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC2" t="inlineStr">
         <is>
           <t>web</t>
@@ -894,6 +918,11 @@
       <c r="R3" t="n">
         <v>0.03104502522097849</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -906,13 +935,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -923,6 +962,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>web</t>
@@ -938,7 +982,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC3" t="inlineStr">
         <is>
           <t>web</t>
@@ -1020,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1032,13 +1085,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1049,6 +1112,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>web</t>
@@ -1064,7 +1132,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC4" t="inlineStr">
         <is>
           <t>web</t>
@@ -1146,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1158,13 +1235,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1175,6 +1262,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>web</t>
@@ -1190,7 +1282,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC5" t="inlineStr">
         <is>
           <t>web</t>
@@ -1272,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0.1611877170661257</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1284,13 +1385,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1301,6 +1412,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>web</t>
@@ -1316,7 +1432,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC6" t="inlineStr">
         <is>
           <t>web</t>
@@ -1398,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0.03225039724426806</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1410,13 +1535,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1427,6 +1562,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>web</t>
@@ -1442,7 +1582,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC7" t="inlineStr">
         <is>
           <t>web</t>
@@ -1524,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0.03322263551180799</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1536,13 +1685,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1553,6 +1712,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>web</t>
@@ -1568,7 +1732,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC8" t="inlineStr">
         <is>
           <t>web</t>
@@ -1650,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1662,13 +1835,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1679,6 +1862,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>web</t>
@@ -1694,7 +1882,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC9" t="inlineStr">
         <is>
           <t>web</t>
@@ -1776,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1788,13 +1985,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -1805,6 +2012,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>web</t>
@@ -1820,7 +2032,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC10" t="inlineStr">
         <is>
           <t>web</t>
@@ -1902,6 +2118,11 @@
       <c r="R11" t="n">
         <v>0.02847154631957574</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1914,13 +2135,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -1931,6 +2162,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>web</t>
@@ -1946,7 +2182,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC11" t="inlineStr">
         <is>
           <t>web</t>
@@ -2028,6 +2268,11 @@
       <c r="R12" t="n">
         <v>0.6523670602909716</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2040,13 +2285,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2057,6 +2312,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2072,7 +2332,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2154,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0.1018220374793344</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2166,13 +2435,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2183,6 +2462,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2198,7 +2482,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2280,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0.02531434082722203</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2292,13 +2585,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2309,6 +2612,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2324,7 +2632,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2406,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0.01142031747568957</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2418,13 +2735,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2435,6 +2762,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2450,7 +2782,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2532,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0.1912581631374754</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2544,13 +2885,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2561,6 +2912,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2576,7 +2932,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2658,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0.229568986315184</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,13 +3035,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -2687,6 +3062,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2702,7 +3082,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2784,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2796,13 +3185,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -2813,6 +3212,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2828,7 +3232,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2910,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0.03346592532948877</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2922,13 +3335,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -2939,6 +3362,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
@@ -2954,7 +3382,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC19" t="inlineStr">
         <is>
           <t>web</t>
@@ -3036,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0.01161075411267424</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3048,13 +3485,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3065,6 +3512,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3080,7 +3532,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3162,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0.05774110447762056</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3174,13 +3635,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3191,6 +3662,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3206,7 +3682,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3288,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3300,13 +3785,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3317,6 +3812,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3332,7 +3832,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3414,6 +3918,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3426,13 +3935,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3443,6 +3962,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3458,7 +3982,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3540,6 +4068,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3552,13 +4085,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -3569,6 +4112,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3584,7 +4132,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3666,6 +4218,11 @@
       <c r="R25" t="n">
         <v>0.01202970036783215</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3678,13 +4235,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -3695,6 +4262,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3710,7 +4282,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3792,6 +4368,11 @@
       <c r="R26" t="n">
         <v>0.5200985586768693</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3804,13 +4385,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -3821,6 +4412,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>web</t>
@@ -3836,7 +4432,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC26" t="inlineStr">
         <is>
           <t>web</t>
@@ -3918,6 +4518,11 @@
       <c r="R27" t="n">
         <v>0.03031680541946678</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3930,13 +4535,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -3947,6 +4562,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>web</t>
@@ -3962,7 +4582,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC27" t="inlineStr">
         <is>
           <t>web</t>
@@ -4044,6 +4668,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4056,13 +4685,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4073,6 +4712,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4088,7 +4732,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4872,6 +5520,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4884,13 +5537,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -4901,6 +5564,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>web</t>
@@ -4916,7 +5584,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC34" t="inlineStr">
         <is>
           <t>web</t>
@@ -4998,6 +5670,11 @@
       <c r="R35" t="n">
         <v>0.124180100883914</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5010,13 +5687,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5027,6 +5714,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5042,7 +5734,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5124,6 +5820,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5136,13 +5837,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5153,6 +5864,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5168,7 +5884,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5250,6 +5970,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5262,13 +5987,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5279,6 +6014,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5294,7 +6034,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5376,6 +6120,11 @@
       <c r="R38" t="n">
         <v>0.1208907877995943</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5388,13 +6137,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5405,6 +6164,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5420,7 +6184,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5502,6 +6270,11 @@
       <c r="R39" t="n">
         <v>0.01075013241475602</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5514,13 +6287,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -5531,6 +6314,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5546,7 +6334,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5628,6 +6420,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5640,13 +6437,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -5657,6 +6464,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5672,7 +6484,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5754,6 +6570,11 @@
       <c r="R41" t="n">
         <v>0.02409236821233664</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5766,13 +6587,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -5783,6 +6614,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5798,7 +6634,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5880,6 +6720,11 @@
       <c r="R42" t="n">
         <v>0.01334216940739287</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5892,13 +6737,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -5909,6 +6764,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>web</t>
@@ -5924,7 +6784,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC42" t="inlineStr">
         <is>
           <t>web</t>
@@ -6006,6 +6870,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6018,13 +6887,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -6035,6 +6914,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>web</t>
@@ -6050,7 +6934,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC43" t="inlineStr">
         <is>
           <t>web</t>
@@ -6132,6 +7020,11 @@
       <c r="R44" t="n">
         <v>0.2889054124145731</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6144,13 +7037,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6161,6 +7064,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>web</t>
@@ -6176,7 +7084,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC44" t="inlineStr">
         <is>
           <t>web</t>
@@ -6258,6 +7170,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6270,13 +7187,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -6287,6 +7214,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>web</t>
@@ -6302,7 +7234,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC45" t="inlineStr">
         <is>
           <t>web</t>
@@ -6384,6 +7320,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6396,13 +7337,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -6413,6 +7364,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>web</t>
@@ -6428,7 +7384,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC46" t="inlineStr">
         <is>
           <t>web</t>
@@ -6510,6 +7470,11 @@
       <c r="R47" t="n">
         <v>0.02284063495137914</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6522,13 +7487,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -6539,6 +7514,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>web</t>
@@ -6554,7 +7534,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC47" t="inlineStr">
         <is>
           <t>web</t>
@@ -6636,6 +7620,11 @@
       <c r="R48" t="n">
         <v>0.2390727039218443</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6648,13 +7637,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -6665,6 +7664,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>web</t>
@@ -6680,7 +7684,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC48" t="inlineStr">
         <is>
           <t>web</t>
@@ -6762,6 +7770,11 @@
       <c r="R49" t="n">
         <v>0.1982641245449317</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6774,13 +7787,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -6791,6 +7814,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>web</t>
@@ -6806,7 +7834,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC49" t="inlineStr">
         <is>
           <t>web</t>
@@ -6888,6 +7920,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6900,13 +7937,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -6917,6 +7964,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>web</t>
@@ -6932,7 +7984,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC50" t="inlineStr">
         <is>
           <t>web</t>
@@ -7014,6 +8070,11 @@
       <c r="R51" t="n">
         <v>0.02509944399711657</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7026,13 +8087,23 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -7043,6 +8114,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>web</t>
@@ -7058,7 +8134,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC51" t="inlineStr">
         <is>
           <t>web</t>
@@ -7140,6 +8220,11 @@
       <c r="R52" t="n">
         <v>0.04063763939435984</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7152,13 +8237,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7169,6 +8264,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>web</t>
@@ -7184,7 +8284,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC52" t="inlineStr">
         <is>
           <t>web</t>
@@ -7266,6 +8370,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7278,13 +8387,23 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -7295,6 +8414,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>web</t>
@@ -7310,7 +8434,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC53" t="inlineStr">
         <is>
           <t>web</t>
@@ -7392,6 +8520,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7404,13 +8537,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -7421,6 +8564,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>web</t>
@@ -7436,7 +8584,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC54" t="inlineStr">
         <is>
           <t>web</t>
@@ -7518,6 +8670,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7530,13 +8687,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -7547,6 +8714,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>web</t>
@@ -7562,7 +8734,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC55" t="inlineStr">
         <is>
           <t>web</t>
@@ -7644,6 +8820,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7656,13 +8837,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -7673,6 +8864,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>web</t>
@@ -7688,7 +8884,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC56" t="inlineStr">
         <is>
           <t>web</t>
@@ -7770,6 +8970,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7782,13 +8987,23 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -7799,6 +9014,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>web</t>
@@ -7814,7 +9034,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB57" t="inlineStr"/>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC57" t="inlineStr">
         <is>
           <t>web</t>
@@ -7896,6 +9120,11 @@
       <c r="R58" t="n">
         <v>0.563440105233275</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7908,13 +9137,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -7925,6 +9164,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>web</t>
@@ -7940,7 +9184,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB58" t="inlineStr"/>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC58" t="inlineStr">
         <is>
           <t>web</t>
@@ -8022,6 +9270,11 @@
       <c r="R59" t="n">
         <v>0.03464777762224775</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8034,13 +9287,23 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
@@ -8051,6 +9314,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>web</t>
@@ -8066,7 +9334,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB59" t="inlineStr"/>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC59" t="inlineStr">
         <is>
           <t>web</t>
@@ -8148,6 +9420,11 @@
       <c r="R60" t="n">
         <v>0.06265687715617979</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8160,13 +9437,23 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
@@ -8177,6 +9464,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>web</t>
@@ -8192,7 +9484,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB60" t="inlineStr"/>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC60" t="inlineStr">
         <is>
           <t>web</t>
@@ -8976,6 +10272,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8988,13 +10289,23 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -9005,6 +10316,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>web</t>
@@ -9020,7 +10336,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB66" t="inlineStr"/>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC66" t="inlineStr">
         <is>
           <t>web</t>
@@ -9102,6 +10422,11 @@
       <c r="R67" t="n">
         <v>0.06209005044195698</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9114,13 +10439,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -9131,6 +10466,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>web</t>
@@ -9146,7 +10486,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB67" t="inlineStr"/>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC67" t="inlineStr">
         <is>
           <t>web</t>
@@ -9228,6 +10572,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9240,13 +10589,23 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -9257,6 +10616,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>web</t>
@@ -9272,7 +10636,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB68" t="inlineStr"/>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC68" t="inlineStr">
         <is>
           <t>web</t>
@@ -9354,6 +10722,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9366,13 +10739,23 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -9383,6 +10766,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>web</t>
@@ -9398,7 +10786,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB69" t="inlineStr"/>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC69" t="inlineStr">
         <is>
           <t>web</t>
@@ -9480,6 +10872,11 @@
       <c r="R70" t="n">
         <v>0.1544715621883704</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9492,13 +10889,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -9509,6 +10916,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>web</t>
@@ -9524,7 +10936,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB70" t="inlineStr"/>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC70" t="inlineStr">
         <is>
           <t>web</t>
@@ -9606,6 +11022,11 @@
       <c r="R71" t="n">
         <v>0.01075013241475602</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9618,13 +11039,23 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -9635,6 +11066,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>web</t>
@@ -9650,7 +11086,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB71" t="inlineStr"/>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC71" t="inlineStr">
         <is>
           <t>web</t>
@@ -9732,6 +11172,11 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9744,13 +11189,23 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -9761,6 +11216,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>web</t>
@@ -9776,7 +11236,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC72" t="inlineStr">
         <is>
           <t>web</t>
@@ -9858,6 +11322,11 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9870,13 +11339,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -9887,6 +11366,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>web</t>
@@ -9902,7 +11386,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC73" t="inlineStr">
         <is>
           <t>web</t>
@@ -9984,6 +11472,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9996,13 +11489,23 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -10013,6 +11516,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>web</t>
@@ -10028,7 +11536,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB74" t="inlineStr"/>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC74" t="inlineStr">
         <is>
           <t>web</t>
@@ -10110,6 +11622,11 @@
       <c r="R75" t="n">
         <v>0.01423577315978787</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10122,13 +11639,23 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -10139,6 +11666,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>web</t>
@@ -10154,7 +11686,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB75" t="inlineStr"/>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC75" t="inlineStr">
         <is>
           <t>web</t>
@@ -10236,6 +11772,11 @@
       <c r="R76" t="n">
         <v>0.5172338835164131</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10248,13 +11789,23 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -10265,6 +11816,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>web</t>
@@ -10280,7 +11836,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC76" t="inlineStr">
         <is>
           <t>web</t>
@@ -10362,6 +11922,11 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10374,13 +11939,23 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -10391,6 +11966,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>web</t>
@@ -10406,7 +11986,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB77" t="inlineStr"/>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC77" t="inlineStr">
         <is>
           <t>web</t>
@@ -10488,6 +12072,11 @@
       <c r="R78" t="n">
         <v>0.02531434082722203</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10500,13 +12089,23 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -10517,6 +12116,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>web</t>
@@ -10532,7 +12136,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB78" t="inlineStr"/>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC78" t="inlineStr">
         <is>
           <t>web</t>
@@ -10614,6 +12222,11 @@
       <c r="R79" t="n">
         <v>0.01142031747568957</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10626,13 +12239,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -10643,6 +12266,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>web</t>
@@ -10658,7 +12286,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB79" t="inlineStr"/>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC79" t="inlineStr">
         <is>
           <t>web</t>
@@ -10740,6 +12372,11 @@
       <c r="R80" t="n">
         <v>0.167350892745291</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10752,13 +12389,23 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -10769,6 +12416,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>web</t>
@@ -10784,7 +12436,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC80" t="inlineStr">
         <is>
           <t>web</t>
@@ -10866,6 +12522,11 @@
       <c r="R81" t="n">
         <v>0.1356544010044269</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10878,13 +12539,23 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
@@ -10895,6 +12566,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>web</t>
@@ -10910,7 +12586,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC81" t="inlineStr">
         <is>
           <t>web</t>
@@ -10992,6 +12672,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11004,13 +12689,23 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>all</t>
@@ -11021,6 +12716,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>web</t>
@@ -11036,7 +12736,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC82" t="inlineStr">
         <is>
           <t>web</t>
@@ -11118,6 +12822,11 @@
       <c r="R83" t="n">
         <v>0.008366481332372193</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11130,13 +12839,23 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>all</t>
@@ -11147,6 +12866,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>web</t>
@@ -11162,7 +12886,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB83" t="inlineStr"/>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC83" t="inlineStr">
         <is>
           <t>web</t>
@@ -11244,6 +12972,11 @@
       <c r="R84" t="n">
         <v>0.05224839350703409</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11256,13 +12989,23 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV84" t="inlineStr">
         <is>
           <t>all</t>
@@ -11273,6 +13016,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>web</t>
@@ -11288,7 +13036,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB84" t="inlineStr"/>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC84" t="inlineStr">
         <is>
           <t>web</t>
@@ -11370,6 +13122,11 @@
       <c r="R85" t="n">
         <v>0.08661165671643084</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11382,13 +13139,23 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>all</t>
@@ -11399,6 +13166,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>web</t>
@@ -11414,7 +13186,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB85" t="inlineStr"/>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC85" t="inlineStr">
         <is>
           <t>web</t>
@@ -11496,6 +13272,11 @@
       <c r="R86" t="n">
         <v>0.1138084989910877</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11508,13 +13289,23 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
       </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV86" t="inlineStr">
         <is>
           <t>all</t>
@@ -11525,6 +13316,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>web</t>
@@ -11540,7 +13336,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB86" t="inlineStr"/>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC86" t="inlineStr">
         <is>
           <t>web</t>
@@ -11622,6 +13422,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11634,13 +13439,23 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
       </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV87" t="inlineStr">
         <is>
           <t>all</t>
@@ -11651,6 +13466,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>web</t>
@@ -11666,7 +13486,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB87" t="inlineStr"/>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC87" t="inlineStr">
         <is>
           <t>web</t>
@@ -11748,6 +13572,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11760,13 +13589,23 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>all</t>
@@ -11777,6 +13616,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>web</t>
@@ -11792,7 +13636,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB88" t="inlineStr"/>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC88" t="inlineStr">
         <is>
           <t>web</t>
@@ -11874,6 +13722,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11886,13 +13739,23 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
       </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV89" t="inlineStr">
         <is>
           <t>all</t>
@@ -11903,6 +13766,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>web</t>
@@ -11918,7 +13786,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB89" t="inlineStr"/>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC89" t="inlineStr">
         <is>
           <t>web</t>
@@ -12000,6 +13872,11 @@
       <c r="R90" t="n">
         <v>0.563440105233275</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12012,13 +13889,23 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV90" t="inlineStr">
         <is>
           <t>all</t>
@@ -12029,6 +13916,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>web</t>
@@ -12044,7 +13936,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC90" t="inlineStr">
         <is>
           <t>web</t>
@@ -12126,6 +14022,11 @@
       <c r="R91" t="n">
         <v>0.03248229152085727</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12138,13 +14039,23 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
       </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV91" t="inlineStr">
         <is>
           <t>all</t>
@@ -12155,6 +14066,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>web</t>
@@ -12170,7 +14086,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB91" t="inlineStr"/>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC91" t="inlineStr">
         <is>
           <t>web</t>
@@ -12252,6 +14172,11 @@
       <c r="R92" t="n">
         <v>0.06265687715617979</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12264,13 +14189,23 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
       </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV92" t="inlineStr">
         <is>
           <t>all</t>
@@ -12281,6 +14216,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>web</t>
@@ -12296,7 +14236,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB92" t="inlineStr"/>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC92" t="inlineStr">
         <is>
           <t>web</t>
@@ -12798,6 +14742,11 @@
       <c r="R96" t="n">
         <v>0.08542940725095212</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12810,12 +14759,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -12933,6 +14892,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12945,13 +14909,23 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
       </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV97" t="inlineStr">
         <is>
           <t>all</t>
@@ -12962,6 +14936,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>web</t>
@@ -12977,7 +14956,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr"/>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC97" t="inlineStr">
         <is>
           <t>web</t>
@@ -13059,6 +15042,11 @@
       <c r="R98" t="n">
         <v>0.09313507566293547</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13071,13 +15059,23 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
       </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV98" t="inlineStr">
         <is>
           <t>all</t>
@@ -13088,6 +15086,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>web</t>
@@ -13103,7 +15106,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB98" t="inlineStr"/>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC98" t="inlineStr">
         <is>
           <t>web</t>
@@ -13185,6 +15192,11 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13197,13 +15209,23 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
       </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV99" t="inlineStr">
         <is>
           <t>all</t>
@@ -13214,6 +15236,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>web</t>
@@ -13229,7 +15256,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB99" t="inlineStr"/>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC99" t="inlineStr">
         <is>
           <t>web</t>
@@ -13311,6 +15342,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13323,13 +15359,23 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>all</t>
@@ -13340,6 +15386,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>web</t>
@@ -13355,7 +15406,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB100" t="inlineStr"/>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC100" t="inlineStr">
         <is>
           <t>web</t>
@@ -13437,6 +15492,11 @@
       <c r="R101" t="n">
         <v>0.08059385853306283</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13449,13 +15509,23 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
       </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV101" t="inlineStr">
         <is>
           <t>all</t>
@@ -13466,6 +15536,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>web</t>
@@ -13481,7 +15556,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB101" t="inlineStr"/>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC101" t="inlineStr">
         <is>
           <t>web</t>
@@ -13563,6 +15642,11 @@
       <c r="R102" t="n">
         <v>0.01075013241475602</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13575,13 +15659,23 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
       </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV102" t="inlineStr">
         <is>
           <t>all</t>
@@ -13592,6 +15686,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>web</t>
@@ -13607,7 +15706,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB102" t="inlineStr"/>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC102" t="inlineStr">
         <is>
           <t>web</t>
@@ -13689,6 +15792,11 @@
       <c r="R103" t="n">
         <v>0.03322263551180799</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13701,13 +15809,23 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
       </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV103" t="inlineStr">
         <is>
           <t>all</t>
@@ -13718,6 +15836,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>web</t>
@@ -13733,7 +15856,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB103" t="inlineStr"/>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC103" t="inlineStr">
         <is>
           <t>web</t>
@@ -13815,6 +15942,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13827,13 +15959,23 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
       </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV104" t="inlineStr">
         <is>
           <t>all</t>
@@ -13844,6 +15986,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>web</t>
@@ -13859,7 +16006,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB104" t="inlineStr"/>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC104" t="inlineStr">
         <is>
           <t>web</t>
@@ -13941,6 +16092,11 @@
       <c r="R105" t="n">
         <v>0.01334216940739287</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13953,13 +16109,23 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
       </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV105" t="inlineStr">
         <is>
           <t>all</t>
@@ -13970,6 +16136,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>web</t>
@@ -13985,7 +16156,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB105" t="inlineStr"/>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC105" t="inlineStr">
         <is>
           <t>web</t>
@@ -14067,6 +16242,11 @@
       <c r="R106" t="n">
         <v>0.01423577315978787</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14079,13 +16259,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>all</t>
@@ -14096,6 +16286,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>web</t>
@@ -14111,7 +16306,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB106" t="inlineStr"/>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC106" t="inlineStr">
         <is>
           <t>web</t>
@@ -14193,6 +16392,11 @@
       <c r="R107" t="n">
         <v>0.4007397656073111</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14205,13 +16409,23 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
       </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV107" t="inlineStr">
         <is>
           <t>all</t>
@@ -14222,6 +16436,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>web</t>
@@ -14237,7 +16456,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB107" t="inlineStr"/>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC107" t="inlineStr">
         <is>
           <t>web</t>
@@ -14319,6 +16542,11 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14331,13 +16559,23 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
       </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV108" t="inlineStr">
         <is>
           <t>all</t>
@@ -14348,6 +16586,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>web</t>
@@ -14363,7 +16606,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB108" t="inlineStr"/>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC108" t="inlineStr">
         <is>
           <t>web</t>
@@ -14445,6 +16692,11 @@
       <c r="R109" t="n">
         <v>0.05062868165444406</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14457,13 +16709,23 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
       </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV109" t="inlineStr">
         <is>
           <t>all</t>
@@ -14474,6 +16736,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>web</t>
@@ -14489,7 +16756,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB109" t="inlineStr"/>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC109" t="inlineStr">
         <is>
           <t>web</t>
@@ -14571,6 +16842,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14583,13 +16859,23 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
       </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV110" t="inlineStr">
         <is>
           <t>all</t>
@@ -14600,6 +16886,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>web</t>
@@ -14615,7 +16906,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB110" t="inlineStr"/>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC110" t="inlineStr">
         <is>
           <t>web</t>
@@ -14697,6 +16992,11 @@
       <c r="R111" t="n">
         <v>0.167350892745291</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14709,13 +17009,23 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
       </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV111" t="inlineStr">
         <is>
           <t>all</t>
@@ -14726,6 +17036,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>web</t>
@@ -14741,7 +17056,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB111" t="inlineStr"/>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC111" t="inlineStr">
         <is>
           <t>web</t>
@@ -14823,6 +17142,11 @@
       <c r="R112" t="n">
         <v>0.3234835716259412</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14835,13 +17159,23 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>all</t>
@@ -14852,6 +17186,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>web</t>
@@ -14867,7 +17206,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB112" t="inlineStr"/>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC112" t="inlineStr">
         <is>
           <t>web</t>
@@ -14949,6 +17292,11 @@
       <c r="R113" t="n">
         <v>0.02947577047453338</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14961,13 +17309,23 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>all</t>
@@ -14978,6 +17336,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>web</t>
@@ -14993,7 +17356,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB113" t="inlineStr"/>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC113" t="inlineStr">
         <is>
           <t>web</t>
@@ -15075,6 +17442,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15087,13 +17459,23 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
       </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV114" t="inlineStr">
         <is>
           <t>all</t>
@@ -15104,6 +17486,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>web</t>
@@ -15119,7 +17506,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB114" t="inlineStr"/>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC114" t="inlineStr">
         <is>
           <t>web</t>
@@ -15201,6 +17592,11 @@
       <c r="R115" t="n">
         <v>0.00580537705633712</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15213,13 +17609,23 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
       </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV115" t="inlineStr">
         <is>
           <t>all</t>
@@ -15230,6 +17636,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>web</t>
@@ -15245,7 +17656,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB115" t="inlineStr"/>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC115" t="inlineStr">
         <is>
           <t>web</t>
@@ -15327,6 +17742,11 @@
       <c r="R116" t="n">
         <v>0.2598349701492925</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15339,13 +17759,23 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
       </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV116" t="inlineStr">
         <is>
           <t>all</t>
@@ -15356,6 +17786,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>web</t>
@@ -15371,7 +17806,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB116" t="inlineStr"/>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC116" t="inlineStr">
         <is>
           <t>web</t>
@@ -15453,6 +17892,11 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15465,13 +17909,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>all</t>
@@ -15482,6 +17936,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>web</t>
@@ -15497,7 +17956,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB117" t="inlineStr"/>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC117" t="inlineStr">
         <is>
           <t>web</t>
@@ -15579,6 +18042,11 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15591,13 +18059,23 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
       </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV118" t="inlineStr">
         <is>
           <t>all</t>
@@ -15608,6 +18086,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>web</t>
@@ -15623,7 +18106,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC118" t="inlineStr">
         <is>
           <t>web</t>
@@ -15705,6 +18192,11 @@
       <c r="R119" t="n">
         <v>0.00890209009502714</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15717,13 +18209,23 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
       </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV119" t="inlineStr">
         <is>
           <t>all</t>
@@ -15734,6 +18236,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>web</t>
@@ -15749,7 +18256,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC119" t="inlineStr">
         <is>
           <t>web</t>
@@ -15831,6 +18342,11 @@
       <c r="R120" t="n">
         <v>0.01202970036783215</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15843,13 +18359,23 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
       </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV120" t="inlineStr">
         <is>
           <t>all</t>
@@ -15860,6 +18386,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>web</t>
@@ -15875,7 +18406,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB120" t="inlineStr"/>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC120" t="inlineStr">
         <is>
           <t>web</t>
@@ -15957,6 +18492,11 @@
       <c r="R121" t="n">
         <v>0.4767570121204635</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15969,13 +18509,23 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
       </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV121" t="inlineStr">
         <is>
           <t>all</t>
@@ -15986,6 +18536,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>web</t>
@@ -16001,7 +18556,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB121" t="inlineStr"/>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC121" t="inlineStr">
         <is>
           <t>web</t>
@@ -16083,6 +18642,11 @@
       <c r="R122" t="n">
         <v>0.03031680541946678</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16095,13 +18659,23 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
       </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV122" t="inlineStr">
         <is>
           <t>all</t>
@@ -16112,6 +18686,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>web</t>
@@ -16127,7 +18706,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB122" t="inlineStr"/>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC122" t="inlineStr">
         <is>
           <t>web</t>
@@ -16209,6 +18792,11 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16221,13 +18809,23 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
       </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV123" t="inlineStr">
         <is>
           <t>all</t>
@@ -16238,6 +18836,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>web</t>
@@ -16253,7 +18856,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB123" t="inlineStr"/>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC123" t="inlineStr">
         <is>
           <t>web</t>
@@ -17037,6 +19644,11 @@
       <c r="R129" t="n">
         <v>0.04434859939257077</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17049,12 +19661,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -17172,6 +19794,11 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17184,13 +19811,23 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
       </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV130" t="inlineStr">
         <is>
           <t>all</t>
@@ -17201,6 +19838,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>web</t>
@@ -17216,7 +19858,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB130" t="inlineStr"/>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC130" t="inlineStr">
         <is>
           <t>web</t>
@@ -17298,6 +19944,11 @@
       <c r="R131" t="n">
         <v>0.09313507566293547</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17310,13 +19961,23 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV131" t="inlineStr">
         <is>
           <t>all</t>
@@ -17327,6 +19988,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>web</t>
@@ -17342,7 +20008,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB131" t="inlineStr"/>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC131" t="inlineStr">
         <is>
           <t>web</t>
@@ -17424,6 +20094,11 @@
       <c r="R132" t="n">
         <v>0</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17436,13 +20111,23 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
       </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV132" t="inlineStr">
         <is>
           <t>all</t>
@@ -17453,6 +20138,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>web</t>
@@ -17468,7 +20158,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC132" t="inlineStr">
         <is>
           <t>web</t>
@@ -17550,6 +20244,11 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17562,13 +20261,23 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
       </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV133" t="inlineStr">
         <is>
           <t>all</t>
@@ -17579,6 +20288,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>web</t>
@@ -17594,7 +20308,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB133" t="inlineStr"/>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC133" t="inlineStr">
         <is>
           <t>web</t>
@@ -17676,6 +20394,11 @@
       <c r="R134" t="n">
         <v>0.06044539389979713</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17688,13 +20411,23 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
       </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV134" t="inlineStr">
         <is>
           <t>all</t>
@@ -17705,6 +20438,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>web</t>
@@ -17720,7 +20458,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB134" t="inlineStr"/>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC134" t="inlineStr">
         <is>
           <t>web</t>
@@ -17802,6 +20544,11 @@
       <c r="R135" t="n">
         <v>0</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17814,13 +20561,23 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
       </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV135" t="inlineStr">
         <is>
           <t>all</t>
@@ -17831,6 +20588,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>web</t>
@@ -17846,7 +20608,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB135" t="inlineStr"/>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC135" t="inlineStr">
         <is>
           <t>web</t>
@@ -17928,6 +20694,11 @@
       <c r="R136" t="n">
         <v>0.03322263551180799</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17940,13 +20711,23 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
       </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV136" t="inlineStr">
         <is>
           <t>all</t>
@@ -17957,6 +20738,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>web</t>
@@ -17972,7 +20758,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB136" t="inlineStr"/>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC136" t="inlineStr">
         <is>
           <t>web</t>
@@ -18054,6 +20844,11 @@
       <c r="R137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18066,13 +20861,23 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>all</t>
@@ -18083,6 +20888,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>web</t>
@@ -18098,7 +20908,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB137" t="inlineStr"/>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC137" t="inlineStr">
         <is>
           <t>web</t>
@@ -18180,6 +20994,11 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18192,13 +21011,23 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
       </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV138" t="inlineStr">
         <is>
           <t>all</t>
@@ -18209,6 +21038,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>web</t>
@@ -18224,7 +21058,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB138" t="inlineStr"/>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC138" t="inlineStr">
         <is>
           <t>web</t>
@@ -18306,6 +21144,11 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18318,13 +21161,23 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
       </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV139" t="inlineStr">
         <is>
           <t>all</t>
@@ -18335,6 +21188,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>web</t>
@@ -18350,7 +21208,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB139" t="inlineStr"/>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC139" t="inlineStr">
         <is>
           <t>web</t>
@@ -18432,6 +21294,11 @@
       <c r="R140" t="n">
         <v>0.22832847110184</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18444,13 +21311,23 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
       </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV140" t="inlineStr">
         <is>
           <t>all</t>
@@ -18461,6 +21338,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>web</t>
@@ -18476,7 +21358,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB140" t="inlineStr"/>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC140" t="inlineStr">
         <is>
           <t>web</t>
@@ -18558,6 +21444,11 @@
       <c r="R141" t="n">
         <v>0</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18570,13 +21461,23 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
       </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV141" t="inlineStr">
         <is>
           <t>all</t>
@@ -18587,6 +21488,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>web</t>
@@ -18602,7 +21508,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB141" t="inlineStr"/>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC141" t="inlineStr">
         <is>
           <t>web</t>
@@ -18684,6 +21594,11 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18696,13 +21611,23 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
       </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV142" t="inlineStr">
         <is>
           <t>all</t>
@@ -18713,6 +21638,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>web</t>
@@ -18728,7 +21658,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB142" t="inlineStr"/>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC142" t="inlineStr">
         <is>
           <t>web</t>
@@ -18810,6 +21744,11 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18822,13 +21761,23 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
       </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV143" t="inlineStr">
         <is>
           <t>all</t>
@@ -18839,6 +21788,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>web</t>
@@ -18854,7 +21808,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB143" t="inlineStr"/>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC143" t="inlineStr">
         <is>
           <t>web</t>
@@ -18936,6 +21894,11 @@
       <c r="R144" t="n">
         <v>0.07172181117655327</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18948,13 +21911,23 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
       </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV144" t="inlineStr">
         <is>
           <t>all</t>
@@ -18965,6 +21938,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>web</t>
@@ -18980,7 +21958,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB144" t="inlineStr"/>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC144" t="inlineStr">
         <is>
           <t>web</t>
@@ -19062,6 +22044,11 @@
       <c r="R145" t="n">
         <v>0.04173981569366982</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19074,13 +22061,23 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
       </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV145" t="inlineStr">
         <is>
           <t>all</t>
@@ -19091,6 +22088,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY145" t="inlineStr">
         <is>
           <t>web</t>
@@ -19106,7 +22108,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB145" t="inlineStr"/>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC145" t="inlineStr">
         <is>
           <t>web</t>
@@ -19188,6 +22194,11 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19200,13 +22211,23 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
       </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV146" t="inlineStr">
         <is>
           <t>all</t>
@@ -19217,6 +22238,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY146" t="inlineStr">
         <is>
           <t>web</t>
@@ -19232,7 +22258,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB146" t="inlineStr"/>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC146" t="inlineStr">
         <is>
           <t>web</t>
@@ -19314,6 +22344,11 @@
       <c r="R147" t="n">
         <v>0.03346592532948877</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19326,13 +22361,23 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
       </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV147" t="inlineStr">
         <is>
           <t>all</t>
@@ -19343,6 +22388,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY147" t="inlineStr">
         <is>
           <t>web</t>
@@ -19358,7 +22408,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB147" t="inlineStr"/>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC147" t="inlineStr">
         <is>
           <t>web</t>
@@ -19440,6 +22494,11 @@
       <c r="R148" t="n">
         <v>0.01741613116901136</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19452,13 +22511,23 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
       </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV148" t="inlineStr">
         <is>
           <t>all</t>
@@ -19469,6 +22538,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY148" t="inlineStr">
         <is>
           <t>web</t>
@@ -19484,7 +22558,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB148" t="inlineStr"/>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC148" t="inlineStr">
         <is>
           <t>web</t>
@@ -19566,6 +22644,11 @@
       <c r="R149" t="n">
         <v>0.1732233134328617</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19578,13 +22661,23 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
       </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV149" t="inlineStr">
         <is>
           <t>all</t>
@@ -19595,6 +22688,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY149" t="inlineStr">
         <is>
           <t>web</t>
@@ -19610,7 +22708,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB149" t="inlineStr"/>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC149" t="inlineStr">
         <is>
           <t>web</t>
@@ -19692,6 +22794,11 @@
       <c r="R150" t="n">
         <v>0.05690424949554383</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19704,13 +22811,23 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
       </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV150" t="inlineStr">
         <is>
           <t>all</t>
@@ -19721,6 +22838,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY150" t="inlineStr">
         <is>
           <t>web</t>
@@ -19736,7 +22858,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB150" t="inlineStr"/>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC150" t="inlineStr">
         <is>
           <t>web</t>
@@ -19818,6 +22944,11 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19830,13 +22961,23 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
       </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV151" t="inlineStr">
         <is>
           <t>all</t>
@@ -19847,6 +22988,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY151" t="inlineStr">
         <is>
           <t>web</t>
@@ -19862,7 +23008,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB151" t="inlineStr"/>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC151" t="inlineStr">
         <is>
           <t>web</t>
@@ -19944,6 +23094,11 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19956,13 +23111,23 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
       </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV152" t="inlineStr">
         <is>
           <t>all</t>
@@ -19973,6 +23138,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY152" t="inlineStr">
         <is>
           <t>web</t>
@@ -19988,7 +23158,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB152" t="inlineStr"/>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC152" t="inlineStr">
         <is>
           <t>web</t>
@@ -20070,6 +23244,11 @@
       <c r="R153" t="n">
         <v>0</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20082,13 +23261,23 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
       </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV153" t="inlineStr">
         <is>
           <t>all</t>
@@ -20099,6 +23288,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY153" t="inlineStr">
         <is>
           <t>web</t>
@@ -20114,7 +23308,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB153" t="inlineStr"/>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC153" t="inlineStr">
         <is>
           <t>web</t>
@@ -20196,6 +23394,11 @@
       <c r="R154" t="n">
         <v>0.3033908258948404</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20208,13 +23411,23 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
       </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV154" t="inlineStr">
         <is>
           <t>all</t>
@@ -20225,6 +23438,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY154" t="inlineStr">
         <is>
           <t>web</t>
@@ -20240,7 +23458,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB154" t="inlineStr"/>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC154" t="inlineStr">
         <is>
           <t>web</t>
@@ -20322,6 +23544,11 @@
       <c r="R155" t="n">
         <v>0.01082743050695242</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20334,13 +23561,23 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>all</t>
@@ -20351,6 +23588,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY155" t="inlineStr">
         <is>
           <t>web</t>
@@ -20366,7 +23608,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB155" t="inlineStr"/>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC155" t="inlineStr">
         <is>
           <t>web</t>
@@ -20448,6 +23694,11 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20460,13 +23711,23 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
       </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV156" t="inlineStr">
         <is>
           <t>all</t>
@@ -20477,6 +23738,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY156" t="inlineStr">
         <is>
           <t>web</t>
@@ -20492,7 +23758,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB156" t="inlineStr"/>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC156" t="inlineStr">
         <is>
           <t>web</t>
